--- a/pressure_sensor/calibration_data_20260202.xlsx
+++ b/pressure_sensor/calibration_data_20260202.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Winston\Documents\GitHub\mae156_ws\MAE-156B-Team-5-QUASAR-Automated-EEG-Headset\pressure_sensor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FC76AB9-073A-445C-9059-52CD3E6DE6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E5FBF4-D70E-4BED-ADF2-9BFE4DFE2D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{92C3B6E5-EE90-44CD-9A99-CEE3390F0301}"/>
   </bookViews>
@@ -123,6 +123,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Forc</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t>e-To-Sensor Calibration Curve</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -210,8 +240,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="1.9982064741907262E-2"/>
-                  <c:y val="-0.14856481481481482"/>
+                  <c:x val="4.2692475940507438E-3"/>
+                  <c:y val="-7.9120370370370369E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -355,6 +385,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Relative Pressure (kPa)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -417,6 +502,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Force</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Applied (gram)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
